--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/186.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/186.xlsx
@@ -426,13 +426,13 @@
         <v>-6.500978433857951</v>
       </c>
       <c r="E2">
-        <v>-17.29557568335895</v>
+        <v>-19.12211756045676</v>
       </c>
       <c r="F2">
-        <v>4.006315254464037</v>
+        <v>2.792703990697719</v>
       </c>
       <c r="G2">
-        <v>-14.26997196532968</v>
+        <v>-16.4994621692974</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.171405860000841</v>
       </c>
       <c r="E3">
-        <v>-17.49354245307827</v>
+        <v>-18.93329377975893</v>
       </c>
       <c r="F3">
-        <v>4.133330052588197</v>
+        <v>3.618419748301369</v>
       </c>
       <c r="G3">
-        <v>-13.98875767449628</v>
+        <v>-15.7228992257867</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.7649242837723</v>
       </c>
       <c r="E4">
-        <v>-17.99046096288795</v>
+        <v>-20.99385360815112</v>
       </c>
       <c r="F4">
-        <v>3.687415480213404</v>
+        <v>2.854218295865218</v>
       </c>
       <c r="G4">
-        <v>-14.07822682296786</v>
+        <v>-15.81227402371041</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.319834416560256</v>
       </c>
       <c r="E5">
-        <v>-16.73480116156711</v>
+        <v>-20.74184402962426</v>
       </c>
       <c r="F5">
-        <v>4.185123570846728</v>
+        <v>3.349598338802847</v>
       </c>
       <c r="G5">
-        <v>-13.38666213617796</v>
+        <v>-15.59380781302836</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.839221109919015</v>
       </c>
       <c r="E6">
-        <v>-18.67515264742569</v>
+        <v>-22.3219780505427</v>
       </c>
       <c r="F6">
-        <v>4.294449957601344</v>
+        <v>3.273604210450484</v>
       </c>
       <c r="G6">
-        <v>-12.3654349798602</v>
+        <v>-14.46602247216532</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.342375764206824</v>
       </c>
       <c r="E7">
-        <v>-20.00846219255606</v>
+        <v>-21.55539797052426</v>
       </c>
       <c r="F7">
-        <v>4.600452030876639</v>
+        <v>3.789868583295013</v>
       </c>
       <c r="G7">
-        <v>-12.42565711376508</v>
+        <v>-14.4784850208479</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.839946135191646</v>
       </c>
       <c r="E8">
-        <v>-20.52599431604866</v>
+        <v>-23.18804417603565</v>
       </c>
       <c r="F8">
-        <v>4.561442186767534</v>
+        <v>3.591463489914674</v>
       </c>
       <c r="G8">
-        <v>-10.87976807929254</v>
+        <v>-13.3691063131832</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.356238806889878</v>
       </c>
       <c r="E9">
-        <v>-21.09833003198208</v>
+        <v>-23.72082367151208</v>
       </c>
       <c r="F9">
-        <v>4.40658583864995</v>
+        <v>3.454919533297316</v>
       </c>
       <c r="G9">
-        <v>-10.32716188624078</v>
+        <v>-11.67843388009618</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.905936253015294</v>
       </c>
       <c r="E10">
-        <v>-21.64247599721776</v>
+        <v>-23.10999139803944</v>
       </c>
       <c r="F10">
-        <v>4.686961966507519</v>
+        <v>3.588220060199854</v>
       </c>
       <c r="G10">
-        <v>-10.41744708418778</v>
+        <v>-12.19827891449132</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.509753122436223</v>
       </c>
       <c r="E11">
-        <v>-21.61716182751488</v>
+        <v>-25.44332838675767</v>
       </c>
       <c r="F11">
-        <v>4.998286875364605</v>
+        <v>3.868371301817431</v>
       </c>
       <c r="G11">
-        <v>-9.668406361017825</v>
+        <v>-11.55361969217458</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.184857213396439</v>
       </c>
       <c r="E12">
-        <v>-23.50804426331367</v>
+        <v>-24.50316736955122</v>
       </c>
       <c r="F12">
-        <v>5.165321921971919</v>
+        <v>4.276501818461669</v>
       </c>
       <c r="G12">
-        <v>-9.779111003851053</v>
+        <v>-10.30456741293525</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.939121985052171</v>
       </c>
       <c r="E13">
-        <v>-24.74991486128116</v>
+        <v>-25.01170141519058</v>
       </c>
       <c r="F13">
-        <v>5.018452202785896</v>
+        <v>4.607562870436962</v>
       </c>
       <c r="G13">
-        <v>-8.281274537881041</v>
+        <v>-10.65445566043529</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.781680166390038</v>
       </c>
       <c r="E14">
-        <v>-24.51538519242391</v>
+        <v>-27.4304091959014</v>
       </c>
       <c r="F14">
-        <v>5.065738494009087</v>
+        <v>4.043828496483052</v>
       </c>
       <c r="G14">
-        <v>-8.01177957825667</v>
+        <v>-10.68423401756103</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.707846859044813</v>
       </c>
       <c r="E15">
-        <v>-26.2681763418328</v>
+        <v>-26.37786051077258</v>
       </c>
       <c r="F15">
-        <v>5.360263450515192</v>
+        <v>4.798945811788242</v>
       </c>
       <c r="G15">
-        <v>-7.180859132263916</v>
+        <v>-9.735180064544926</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.706193932580584</v>
       </c>
       <c r="E16">
-        <v>-25.76514892058677</v>
+        <v>-28.17051581687099</v>
       </c>
       <c r="F16">
-        <v>6.211742935951211</v>
+        <v>4.703915538332298</v>
       </c>
       <c r="G16">
-        <v>-7.206883330748127</v>
+        <v>-8.703832570513615</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.762870409657374</v>
       </c>
       <c r="E17">
-        <v>-28.66718073213625</v>
+        <v>-28.63939854409919</v>
       </c>
       <c r="F17">
-        <v>6.178684658672328</v>
+        <v>5.252210363316589</v>
       </c>
       <c r="G17">
-        <v>-8.01145845533936</v>
+        <v>-9.218662128416756</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.859931350985111</v>
       </c>
       <c r="E18">
-        <v>-28.5288267942539</v>
+        <v>-29.57464163853331</v>
       </c>
       <c r="F18">
-        <v>5.931814996867711</v>
+        <v>5.22835658481824</v>
       </c>
       <c r="G18">
-        <v>-6.842587589061186</v>
+        <v>-8.587586074447646</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.983876430970928</v>
       </c>
       <c r="E19">
-        <v>-30.10669884240551</v>
+        <v>-30.87934028488322</v>
       </c>
       <c r="F19">
-        <v>6.67069140801007</v>
+        <v>5.474166747365428</v>
       </c>
       <c r="G19">
-        <v>-6.634718434650348</v>
+        <v>-8.386718723852367</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.126099916192634</v>
       </c>
       <c r="E20">
-        <v>-30.91996975368004</v>
+        <v>-32.10786094147609</v>
       </c>
       <c r="F20">
-        <v>6.593213347214941</v>
+        <v>5.631903856543197</v>
       </c>
       <c r="G20">
-        <v>-7.529942917197905</v>
+        <v>-9.274636832394753</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.278661634465013</v>
       </c>
       <c r="E21">
-        <v>-30.76448459862667</v>
+        <v>-32.89489613858718</v>
       </c>
       <c r="F21">
-        <v>6.624375928513043</v>
+        <v>5.384278767016915</v>
       </c>
       <c r="G21">
-        <v>-6.776492547369637</v>
+        <v>-8.514429639120833</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.438193998603427</v>
       </c>
       <c r="E22">
-        <v>-31.2519204838643</v>
+        <v>-34.14801773022673</v>
       </c>
       <c r="F22">
-        <v>6.985497302469292</v>
+        <v>5.730198147890861</v>
       </c>
       <c r="G22">
-        <v>-6.528171837014444</v>
+        <v>-7.801338129961819</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.603208737875215</v>
       </c>
       <c r="E23">
-        <v>-30.84085731276603</v>
+        <v>-33.54336229530055</v>
       </c>
       <c r="F23">
-        <v>6.717622949108202</v>
+        <v>5.190043571311929</v>
       </c>
       <c r="G23">
-        <v>-5.402748570393665</v>
+        <v>-8.432324799201368</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.770200379812751</v>
       </c>
       <c r="E24">
-        <v>-30.35420258929474</v>
+        <v>-34.42134057167068</v>
       </c>
       <c r="F24">
-        <v>6.873751013075885</v>
+        <v>5.71343620448185</v>
       </c>
       <c r="G24">
-        <v>-5.420870496675636</v>
+        <v>-7.019963308509797</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.941241632740805</v>
       </c>
       <c r="E25">
-        <v>-32.19581296365307</v>
+        <v>-33.28431773240278</v>
       </c>
       <c r="F25">
-        <v>6.937175267577404</v>
+        <v>5.416199943448513</v>
       </c>
       <c r="G25">
-        <v>-6.241336239855371</v>
+        <v>-7.50257463722475</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.114995925388409</v>
       </c>
       <c r="E26">
-        <v>-32.53470358025408</v>
+        <v>-34.51044509048261</v>
       </c>
       <c r="F26">
-        <v>7.17443975300488</v>
+        <v>5.571832307464663</v>
       </c>
       <c r="G26">
-        <v>-5.300502371413274</v>
+        <v>-7.887253407796984</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.290319990085282</v>
       </c>
       <c r="E27">
-        <v>-32.12146447739514</v>
+        <v>-34.29378704429663</v>
       </c>
       <c r="F27">
-        <v>6.651994175972392</v>
+        <v>5.756848751035876</v>
       </c>
       <c r="G27">
-        <v>-5.786053464567101</v>
+        <v>-8.003619083502366</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.469165668854612</v>
       </c>
       <c r="E28">
-        <v>-31.87201348668261</v>
+        <v>-35.22152419306303</v>
       </c>
       <c r="F28">
-        <v>6.637208697545849</v>
+        <v>5.143184880685906</v>
       </c>
       <c r="G28">
-        <v>-4.907990850095126</v>
+        <v>-7.002516733517838</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.649093199070594</v>
       </c>
       <c r="E29">
-        <v>-32.71538290044911</v>
+        <v>-33.295072858171</v>
       </c>
       <c r="F29">
-        <v>6.605943175363243</v>
+        <v>5.458895071222845</v>
       </c>
       <c r="G29">
-        <v>-4.839750574894128</v>
+        <v>-8.340930568498708</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.830837647620703</v>
       </c>
       <c r="E30">
-        <v>-30.08216809870596</v>
+        <v>-33.26358864263267</v>
       </c>
       <c r="F30">
-        <v>6.449729591276127</v>
+        <v>5.474116068776134</v>
       </c>
       <c r="G30">
-        <v>-5.844385276969059</v>
+        <v>-6.54168217336021</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.013535062053615</v>
       </c>
       <c r="E31">
-        <v>-31.99989985689623</v>
+        <v>-34.09488288045772</v>
       </c>
       <c r="F31">
-        <v>6.00808785746119</v>
+        <v>5.29012745034404</v>
       </c>
       <c r="G31">
-        <v>-5.926645712528869</v>
+        <v>-7.454558484723162</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.193164038163403</v>
       </c>
       <c r="E32">
-        <v>-31.34773167268158</v>
+        <v>-33.84904108352931</v>
       </c>
       <c r="F32">
-        <v>6.809474724791859</v>
+        <v>4.868231361882803</v>
       </c>
       <c r="G32">
-        <v>-5.512155479375499</v>
+        <v>-6.864384220891748</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.36965227111036</v>
       </c>
       <c r="E33">
-        <v>-31.80560794383414</v>
+        <v>-33.82354803910314</v>
       </c>
       <c r="F33">
-        <v>6.193459051157462</v>
+        <v>5.112359628747793</v>
       </c>
       <c r="G33">
-        <v>-5.493894510180879</v>
+        <v>-7.070584860350793</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.537599524846962</v>
       </c>
       <c r="E34">
-        <v>-30.00659918870296</v>
+        <v>-31.55905744072353</v>
       </c>
       <c r="F34">
-        <v>6.430905662765213</v>
+        <v>4.403725665766666</v>
       </c>
       <c r="G34">
-        <v>-5.560178252968167</v>
+        <v>-6.643891956339669</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.694006466074562</v>
       </c>
       <c r="E35">
-        <v>-29.21696464751147</v>
+        <v>-32.99063713605734</v>
       </c>
       <c r="F35">
-        <v>6.134461254689596</v>
+        <v>5.354756905047209</v>
       </c>
       <c r="G35">
-        <v>-5.086760309215769</v>
+        <v>-7.857796173588549</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.837887646396604</v>
       </c>
       <c r="E36">
-        <v>-28.32780330457941</v>
+        <v>-32.75556857879319</v>
       </c>
       <c r="F36">
-        <v>6.175941680026787</v>
+        <v>5.486442051915999</v>
       </c>
       <c r="G36">
-        <v>-6.086316634433458</v>
+        <v>-6.533902391342923</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.965251989659586</v>
       </c>
       <c r="E37">
-        <v>-29.16778089131417</v>
+        <v>-30.27256552412146</v>
       </c>
       <c r="F37">
-        <v>5.996759609048052</v>
+        <v>5.079152483112859</v>
       </c>
       <c r="G37">
-        <v>-5.780058066595481</v>
+        <v>-8.577634574556598</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.079283899808904</v>
       </c>
       <c r="E38">
-        <v>-27.84231013469108</v>
+        <v>-30.4568517738636</v>
       </c>
       <c r="F38">
-        <v>6.758642516024</v>
+        <v>4.747747766953916</v>
       </c>
       <c r="G38">
-        <v>-4.972506761564443</v>
+        <v>-7.903981594406921</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.178459969037689</v>
       </c>
       <c r="E39">
-        <v>-28.29018074252368</v>
+        <v>-30.61799752142655</v>
       </c>
       <c r="F39">
-        <v>6.012761373617652</v>
+        <v>5.500421424031583</v>
       </c>
       <c r="G39">
-        <v>-5.455449144833323</v>
+        <v>-7.020536032888091</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.26378275662675</v>
       </c>
       <c r="E40">
-        <v>-26.24212403086667</v>
+        <v>-28.74474443493963</v>
       </c>
       <c r="F40">
-        <v>6.251923138731825</v>
+        <v>5.301583978936329</v>
       </c>
       <c r="G40">
-        <v>-5.823062053150614</v>
+        <v>-6.714678041060365</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.339303254988898</v>
       </c>
       <c r="E41">
-        <v>-27.50842574610554</v>
+        <v>-29.88716747946167</v>
       </c>
       <c r="F41">
-        <v>6.063471637030023</v>
+        <v>4.954636772923263</v>
       </c>
       <c r="G41">
-        <v>-5.726261701582324</v>
+        <v>-7.869343356429527</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.405829084456861</v>
       </c>
       <c r="E42">
-        <v>-25.57935468900007</v>
+        <v>-27.777910705828</v>
       </c>
       <c r="F42">
-        <v>5.9246028001288</v>
+        <v>5.18891438899422</v>
       </c>
       <c r="G42">
-        <v>-5.626961888131885</v>
+        <v>-8.779107754985564</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.469798534209766</v>
       </c>
       <c r="E43">
-        <v>-24.82821217687378</v>
+        <v>-28.33645268993406</v>
       </c>
       <c r="F43">
-        <v>6.192565841021154</v>
+        <v>4.892786722101691</v>
       </c>
       <c r="G43">
-        <v>-6.079573053169963</v>
+        <v>-7.492272219506539</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.53360328299271</v>
       </c>
       <c r="E44">
-        <v>-25.03317543893495</v>
+        <v>-28.68473309738998</v>
       </c>
       <c r="F44">
-        <v>6.104630570066379</v>
+        <v>5.145889850389477</v>
       </c>
       <c r="G44">
-        <v>-6.148339705111704</v>
+        <v>-8.72638400672713</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.59972961924628</v>
       </c>
       <c r="E45">
-        <v>-23.04783809228417</v>
+        <v>-27.04726859553443</v>
       </c>
       <c r="F45">
-        <v>5.798261077018703</v>
+        <v>4.69669542306381</v>
       </c>
       <c r="G45">
-        <v>-6.201656041021667</v>
+        <v>-7.587324603030093</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.673285606098374</v>
       </c>
       <c r="E46">
-        <v>-23.97637451671293</v>
+        <v>-28.23091207471129</v>
       </c>
       <c r="F46">
-        <v>6.186704545428113</v>
+        <v>5.180538168407462</v>
       </c>
       <c r="G46">
-        <v>-6.220900242241449</v>
+        <v>-6.974867057173845</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.753280475348086</v>
       </c>
       <c r="E47">
-        <v>-24.05344008737546</v>
+        <v>-26.7242525445673</v>
       </c>
       <c r="F47">
-        <v>6.086389445332347</v>
+        <v>5.029959409967478</v>
       </c>
       <c r="G47">
-        <v>-6.21172672055213</v>
+        <v>-8.538275498640202</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.84197445902175</v>
       </c>
       <c r="E48">
-        <v>-23.10976044586505</v>
+        <v>-25.87894947239952</v>
       </c>
       <c r="F48">
-        <v>6.061845171054867</v>
+        <v>5.319959718673173</v>
       </c>
       <c r="G48">
-        <v>-6.785119829044977</v>
+        <v>-9.29209333902333</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.939348601758518</v>
       </c>
       <c r="E49">
-        <v>-22.17777785271646</v>
+        <v>-24.642372660547</v>
       </c>
       <c r="F49">
-        <v>6.055090665325517</v>
+        <v>5.297049828900426</v>
       </c>
       <c r="G49">
-        <v>-6.444305786868087</v>
+        <v>-8.567199735016814</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.04207914736359</v>
       </c>
       <c r="E50">
-        <v>-22.98339790715502</v>
+        <v>-22.9914133061486</v>
       </c>
       <c r="F50">
-        <v>6.200465366127366</v>
+        <v>4.61034860914222</v>
       </c>
       <c r="G50">
-        <v>-6.593336615409458</v>
+        <v>-8.771599437702497</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.153722357505091</v>
       </c>
       <c r="E51">
-        <v>-21.32882030202449</v>
+        <v>-24.52442855501723</v>
       </c>
       <c r="F51">
-        <v>6.009345319958049</v>
+        <v>4.894338753898822</v>
       </c>
       <c r="G51">
-        <v>-6.438777175817505</v>
+        <v>-9.300445845418912</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.270356003895816</v>
       </c>
       <c r="E52">
-        <v>-20.03084191110196</v>
+        <v>-22.08510263214948</v>
       </c>
       <c r="F52">
-        <v>5.682698056369086</v>
+        <v>5.093882531832361</v>
       </c>
       <c r="G52">
-        <v>-6.551199991785615</v>
+        <v>-8.982947975475108</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.39123447174658</v>
       </c>
       <c r="E53">
-        <v>-19.92051469885309</v>
+        <v>-22.41949420982388</v>
       </c>
       <c r="F53">
-        <v>6.139221874671407</v>
+        <v>5.297030824429441</v>
       </c>
       <c r="G53">
-        <v>-6.844726201479555</v>
+        <v>-8.205999353409092</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.516473405193624</v>
       </c>
       <c r="E54">
-        <v>-21.01611558637283</v>
+        <v>-22.04479468500721</v>
       </c>
       <c r="F54">
-        <v>6.048858782548264</v>
+        <v>4.560781781400796</v>
       </c>
       <c r="G54">
-        <v>-6.288478408334592</v>
+        <v>-9.187821086172905</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.641586727866042</v>
       </c>
       <c r="E55">
-        <v>-19.26835557158646</v>
+        <v>-20.86508644974301</v>
       </c>
       <c r="F55">
-        <v>5.960535503644206</v>
+        <v>4.796581338856491</v>
       </c>
       <c r="G55">
-        <v>-6.862219124109064</v>
+        <v>-8.746796830522277</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.770000584619432</v>
       </c>
       <c r="E56">
-        <v>-19.14792080535247</v>
+        <v>-20.32920494957133</v>
       </c>
       <c r="F56">
-        <v>5.984903986565072</v>
+        <v>4.891711385785108</v>
       </c>
       <c r="G56">
-        <v>-7.575270906721607</v>
+        <v>-9.288024678555566</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.899192897945852</v>
       </c>
       <c r="E57">
-        <v>-17.64764642355929</v>
+        <v>-18.35845834617327</v>
       </c>
       <c r="F57">
-        <v>5.999762315463725</v>
+        <v>4.987931022383546</v>
       </c>
       <c r="G57">
-        <v>-7.652737672340552</v>
+        <v>-8.379644088034945</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.029439588862164</v>
       </c>
       <c r="E58">
-        <v>-16.66044814683517</v>
+        <v>-21.51614968629979</v>
       </c>
       <c r="F58">
-        <v>5.951676252753237</v>
+        <v>4.712637006808623</v>
       </c>
       <c r="G58">
-        <v>-6.747197529892626</v>
+        <v>-8.99747795984697</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.164550102566516</v>
       </c>
       <c r="E59">
-        <v>-19.05911743006205</v>
+        <v>-18.622789902475</v>
       </c>
       <c r="F59">
-        <v>6.105188034548614</v>
+        <v>5.909689041523106</v>
       </c>
       <c r="G59">
-        <v>-7.353666298868332</v>
+        <v>-10.56981825317828</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.302124956682609</v>
       </c>
       <c r="E60">
-        <v>-17.77282703055332</v>
+        <v>-18.87317828730711</v>
       </c>
       <c r="F60">
-        <v>5.851459342424229</v>
+        <v>5.024028431314158</v>
       </c>
       <c r="G60">
-        <v>-8.240283363013784</v>
+        <v>-9.118144034207864</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.445356258199489</v>
       </c>
       <c r="E61">
-        <v>-17.2091135291305</v>
+        <v>-19.60600312207237</v>
       </c>
       <c r="F61">
-        <v>5.931164093736466</v>
+        <v>5.316763800135816</v>
       </c>
       <c r="G61">
-        <v>-8.064754927976088</v>
+        <v>-9.89023608596777</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.59467040660447</v>
       </c>
       <c r="E62">
-        <v>-16.98836400667859</v>
+        <v>-17.63428742523666</v>
       </c>
       <c r="F62">
-        <v>5.882696357900357</v>
+        <v>5.480571254087464</v>
       </c>
       <c r="G62">
-        <v>-8.247069981369291</v>
+        <v>-8.580127415347668</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.747187021868108</v>
       </c>
       <c r="E63">
-        <v>-16.36135602405056</v>
+        <v>-17.74985861038642</v>
       </c>
       <c r="F63">
-        <v>5.600429285179753</v>
+        <v>5.673727946064037</v>
       </c>
       <c r="G63">
-        <v>-7.914138348121405</v>
+        <v>-9.635201589258935</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.907805790983075</v>
       </c>
       <c r="E64">
-        <v>-15.29586496020783</v>
+        <v>-18.77538136263746</v>
       </c>
       <c r="F64">
-        <v>6.106269705688859</v>
+        <v>5.271864153727193</v>
       </c>
       <c r="G64">
-        <v>-8.932554851276322</v>
+        <v>-10.56858341969213</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.072077522597333</v>
       </c>
       <c r="E65">
-        <v>-16.84640993196015</v>
+        <v>-18.48431369579444</v>
       </c>
       <c r="F65">
-        <v>5.907723662482046</v>
+        <v>5.026535437778299</v>
       </c>
       <c r="G65">
-        <v>-9.197001228953305</v>
+        <v>-10.35008079300916</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.240002134780076</v>
       </c>
       <c r="E66">
-        <v>-15.4380726294707</v>
+        <v>-18.68327672979545</v>
       </c>
       <c r="F66">
-        <v>5.631564943477293</v>
+        <v>4.644268422439102</v>
       </c>
       <c r="G66">
-        <v>-7.965799411261732</v>
+        <v>-10.63161289621432</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.410880930068579</v>
       </c>
       <c r="E67">
-        <v>-15.95929998775356</v>
+        <v>-18.33760925184195</v>
       </c>
       <c r="F67">
-        <v>5.948002055029417</v>
+        <v>4.734965676510404</v>
       </c>
       <c r="G67">
-        <v>-7.980802803645709</v>
+        <v>-11.31115533687836</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.578250123261165</v>
       </c>
       <c r="E68">
-        <v>-15.08154587084682</v>
+        <v>-18.12218068634906</v>
       </c>
       <c r="F68">
-        <v>5.818496087500272</v>
+        <v>4.992813587720846</v>
       </c>
       <c r="G68">
-        <v>-8.00691638685948</v>
+        <v>-10.00786970061469</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.743902318199392</v>
       </c>
       <c r="E69">
-        <v>-15.12010129854812</v>
+        <v>-16.6093397891846</v>
       </c>
       <c r="F69">
-        <v>5.586394483357129</v>
+        <v>4.638611424909152</v>
       </c>
       <c r="G69">
-        <v>-9.199490759198836</v>
+        <v>-12.16258792303243</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.900210694520695</v>
       </c>
       <c r="E70">
-        <v>-14.71725730777378</v>
+        <v>-17.56448552688243</v>
       </c>
       <c r="F70">
-        <v>5.567643405318326</v>
+        <v>4.76845313809237</v>
       </c>
       <c r="G70">
-        <v>-9.332455510238125</v>
+        <v>-10.02963984808094</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.044291083356612</v>
       </c>
       <c r="E71">
-        <v>-16.03866602321199</v>
+        <v>-19.32809972916965</v>
       </c>
       <c r="F71">
-        <v>5.498082290394478</v>
+        <v>5.111615286967536</v>
       </c>
       <c r="G71">
-        <v>-8.170652658686294</v>
+        <v>-10.69102063591654</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.173323442026977</v>
       </c>
       <c r="E72">
-        <v>-15.41317507937653</v>
+        <v>-16.19759734698519</v>
       </c>
       <c r="F72">
-        <v>5.766040580169087</v>
+        <v>4.63343429027158</v>
       </c>
       <c r="G72">
-        <v>-9.208713939071245</v>
+        <v>-10.63916425058939</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.279390179952991</v>
       </c>
       <c r="E73">
-        <v>-15.16827520504172</v>
+        <v>-18.22862699637336</v>
       </c>
       <c r="F73">
-        <v>5.509285426040297</v>
+        <v>4.562129515134835</v>
       </c>
       <c r="G73">
-        <v>-8.503643881753886</v>
+        <v>-12.24438488221675</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.360612856710661</v>
       </c>
       <c r="E74">
-        <v>-15.02707285700855</v>
+        <v>-17.72567203071145</v>
       </c>
       <c r="F74">
-        <v>5.106237021678704</v>
+        <v>4.17633717042787</v>
       </c>
       <c r="G74">
-        <v>-8.663549852391764</v>
+        <v>-11.34334377115669</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.40880909108304</v>
       </c>
       <c r="E75">
-        <v>-15.25054852081307</v>
+        <v>-16.89899004366321</v>
       </c>
       <c r="F75">
-        <v>5.218144849075486</v>
+        <v>4.472390403142374</v>
       </c>
       <c r="G75">
-        <v>-8.212739624127048</v>
+        <v>-10.2678501523592</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.418313427141435</v>
       </c>
       <c r="E76">
-        <v>-14.26157055380394</v>
+        <v>-18.69443488975035</v>
       </c>
       <c r="F76">
-        <v>4.955290843466339</v>
+        <v>4.745023792779359</v>
       </c>
       <c r="G76">
-        <v>-8.43862807790814</v>
+        <v>-9.914300441492731</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.386217384418703</v>
       </c>
       <c r="E77">
-        <v>-15.60200791702238</v>
+        <v>-18.12194067722665</v>
       </c>
       <c r="F77">
-        <v>5.095387052452028</v>
+        <v>4.112472645681859</v>
       </c>
       <c r="G77">
-        <v>-8.330892994423637</v>
+        <v>-10.98581809509756</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.30482752468545</v>
       </c>
       <c r="E78">
-        <v>-15.67751569262627</v>
+        <v>-16.89735073607244</v>
       </c>
       <c r="F78">
-        <v>5.166406760523995</v>
+        <v>3.961898638359623</v>
       </c>
       <c r="G78">
-        <v>-7.716389531424119</v>
+        <v>-10.31724349180512</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.174583603061787</v>
       </c>
       <c r="E79">
-        <v>-15.53528085251935</v>
+        <v>-17.93249649558977</v>
       </c>
       <c r="F79">
-        <v>4.90889301126171</v>
+        <v>4.467702633632674</v>
       </c>
       <c r="G79">
-        <v>-7.726377447316101</v>
+        <v>-10.17973667228596</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.992753115157717</v>
       </c>
       <c r="E80">
-        <v>-17.50066121421833</v>
+        <v>-19.85871008559641</v>
       </c>
       <c r="F80">
-        <v>4.362921482855369</v>
+        <v>3.911999232375956</v>
       </c>
       <c r="G80">
-        <v>-7.41417976078067</v>
+        <v>-9.876609880528129</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.761006420241284</v>
       </c>
       <c r="E81">
-        <v>-16.80118859051955</v>
+        <v>-17.41101101428848</v>
       </c>
       <c r="F81">
-        <v>4.683813559147625</v>
+        <v>4.641145354373855</v>
       </c>
       <c r="G81">
-        <v>-7.554291979639245</v>
+        <v>-10.08924290996998</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.487291362919226</v>
       </c>
       <c r="E82">
-        <v>-15.68131508231871</v>
+        <v>-18.6670104511599</v>
       </c>
       <c r="F82">
-        <v>4.55679400990572</v>
+        <v>4.144477758526975</v>
       </c>
       <c r="G82">
-        <v>-6.513618678823808</v>
+        <v>-9.490408259007831</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.173744914117266</v>
       </c>
       <c r="E83">
-        <v>-18.03797824065044</v>
+        <v>-19.21764571964857</v>
       </c>
       <c r="F83">
-        <v>4.255645995261247</v>
+        <v>3.96832056584673</v>
       </c>
       <c r="G83">
-        <v>-6.931975629167048</v>
+        <v>-10.33032345723078</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.833943637303165</v>
       </c>
       <c r="E84">
-        <v>-19.23528412590844</v>
+        <v>-19.33776349270202</v>
       </c>
       <c r="F84">
-        <v>4.522973970081511</v>
+        <v>3.943126972143919</v>
       </c>
       <c r="G84">
-        <v>-6.707507399422304</v>
+        <v>-10.32908200265356</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.477212607061156</v>
       </c>
       <c r="E85">
-        <v>-19.42066173788644</v>
+        <v>-21.13307248456893</v>
       </c>
       <c r="F85">
-        <v>4.721428158345227</v>
+        <v>3.457828801063978</v>
       </c>
       <c r="G85">
-        <v>-6.54136767153398</v>
+        <v>-10.15818833137084</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.115214724618678</v>
       </c>
       <c r="E86">
-        <v>-21.04541934167646</v>
+        <v>-21.93366140438497</v>
       </c>
       <c r="F86">
-        <v>4.358121270225672</v>
+        <v>3.739311939356439</v>
       </c>
       <c r="G86">
-        <v>-6.841028322112189</v>
+        <v>-9.748018360146219</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.765043557050664</v>
       </c>
       <c r="E87">
-        <v>-21.11955951813004</v>
+        <v>-22.63332875246607</v>
       </c>
       <c r="F87">
-        <v>4.333922243837757</v>
+        <v>3.646994554133643</v>
       </c>
       <c r="G87">
-        <v>-6.211561193275166</v>
+        <v>-7.263533386016135</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.435813373535368</v>
       </c>
       <c r="E88">
-        <v>-22.43153542221027</v>
+        <v>-24.86247913968982</v>
       </c>
       <c r="F88">
-        <v>4.047445680793915</v>
+        <v>3.614253018037848</v>
       </c>
       <c r="G88">
-        <v>-5.197375567319438</v>
+        <v>-8.663506815299753</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.143961597170938</v>
       </c>
       <c r="E89">
-        <v>-24.10086226718379</v>
+        <v>-26.85505298780485</v>
       </c>
       <c r="F89">
-        <v>4.063830702195052</v>
+        <v>3.445429967452003</v>
       </c>
       <c r="G89">
-        <v>-5.774542697727055</v>
+        <v>-7.273041272804922</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.902907453798578</v>
       </c>
       <c r="E90">
-        <v>-24.55327946292009</v>
+        <v>-25.85003516586055</v>
       </c>
       <c r="F90">
-        <v>4.0421101755648</v>
+        <v>3.148668818193297</v>
       </c>
       <c r="G90">
-        <v>-4.995097924324429</v>
+        <v>-7.400454238974852</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.720560299756416</v>
       </c>
       <c r="E91">
-        <v>-26.99363334938758</v>
+        <v>-29.51673151292322</v>
       </c>
       <c r="F91">
-        <v>3.794527846098235</v>
+        <v>3.373990577312445</v>
       </c>
       <c r="G91">
-        <v>-4.290315884468986</v>
+        <v>-8.370844657991562</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.608225673224204</v>
       </c>
       <c r="E92">
-        <v>-28.5840288924074</v>
+        <v>-30.44771104907912</v>
       </c>
       <c r="F92">
-        <v>3.173273273295564</v>
+        <v>2.970264346819043</v>
       </c>
       <c r="G92">
-        <v>-5.095079710155958</v>
+        <v>-7.544217989563243</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.569244508833082</v>
       </c>
       <c r="E93">
-        <v>-29.41279850597318</v>
+        <v>-30.67896889546583</v>
       </c>
       <c r="F93">
-        <v>3.371079725839867</v>
+        <v>2.540224842540616</v>
       </c>
       <c r="G93">
-        <v>-5.676044036297119</v>
+        <v>-6.432410996745486</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.603090900022318</v>
       </c>
       <c r="E94">
-        <v>-31.40801471867169</v>
+        <v>-33.7432332883401</v>
       </c>
       <c r="F94">
-        <v>3.16875020920107</v>
+        <v>2.528716051653118</v>
       </c>
       <c r="G94">
-        <v>-4.365286498751321</v>
+        <v>-7.03939290027978</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.711174938839342</v>
       </c>
       <c r="E95">
-        <v>-33.07929560017951</v>
+        <v>-34.41185568286161</v>
       </c>
       <c r="F95">
-        <v>2.771227354778445</v>
+        <v>2.83249301811722</v>
       </c>
       <c r="G95">
-        <v>-4.426958651602404</v>
+        <v>-7.977174445734668</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.888280531463575</v>
       </c>
       <c r="E96">
-        <v>-35.35930754322041</v>
+        <v>-36.77211218531843</v>
       </c>
       <c r="F96">
-        <v>2.804828843186324</v>
+        <v>1.679127511080133</v>
       </c>
       <c r="G96">
-        <v>-4.845659898681728</v>
+        <v>-6.871995165086532</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.124964774822818</v>
       </c>
       <c r="E97">
-        <v>-36.78737314272428</v>
+        <v>-38.55144019241227</v>
       </c>
       <c r="F97">
-        <v>1.926570474426139</v>
+        <v>1.614813213854137</v>
       </c>
       <c r="G97">
-        <v>-4.191383541573406</v>
+        <v>-6.36970595368615</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.425234375971258</v>
       </c>
       <c r="E98">
-        <v>-39.80324852658959</v>
+        <v>-38.24366924919196</v>
       </c>
       <c r="F98">
-        <v>2.050981660025315</v>
+        <v>1.419290465239899</v>
       </c>
       <c r="G98">
-        <v>-4.346912971008366</v>
+        <v>-6.514489352300637</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.763529344665153</v>
       </c>
       <c r="E99">
-        <v>-41.32067676792382</v>
+        <v>-42.7127998692288</v>
       </c>
       <c r="F99">
-        <v>1.593951055830054</v>
+        <v>1.556973106410458</v>
       </c>
       <c r="G99">
-        <v>-3.998597232639487</v>
+        <v>-6.667479593306976</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.159633852952673</v>
       </c>
       <c r="E100">
-        <v>-42.84435203915163</v>
+        <v>-43.83356322257216</v>
       </c>
       <c r="F100">
-        <v>0.8995197674985874</v>
+        <v>1.162042778571407</v>
       </c>
       <c r="G100">
-        <v>-4.92895653499533</v>
+        <v>-6.543754574867794</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.565137950969467</v>
       </c>
       <c r="E101">
-        <v>-46.49437454491806</v>
+        <v>-46.21081282374276</v>
       </c>
       <c r="F101">
-        <v>1.071248918439264</v>
+        <v>0.8814021718259601</v>
       </c>
       <c r="G101">
-        <v>-4.455565075607247</v>
+        <v>-6.715552025082733</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.037039554385563</v>
       </c>
       <c r="E102">
-        <v>-47.8337477167447</v>
+        <v>-49.32991703684992</v>
       </c>
       <c r="F102">
-        <v>0.8817315826563715</v>
+        <v>0.5783521263770447</v>
       </c>
       <c r="G102">
-        <v>-4.299141798876683</v>
+        <v>-6.895086220222948</v>
       </c>
     </row>
   </sheetData>
